--- a/AAII_Financials/Yearly/SCTH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SCTH_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>SCTH</t>
   </si>
@@ -1623,7 +1623,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3100</v>
+        <v>1900</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>4</v>
@@ -1713,7 +1713,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>8700</v>
+        <v>7500</v>
       </c>
       <c r="E46" s="3">
         <v>0</v>
@@ -1803,7 +1803,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9500</v>
+        <v>9800</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -1953,7 +1953,7 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>18900</v>
+        <v>19200</v>
       </c>
       <c r="E54" s="3">
         <v>0</v>
@@ -2160,8 +2160,8 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>4</v>
+      <c r="D62" s="3">
+        <v>700</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>4</v>
@@ -2281,7 +2281,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>7100</v>
+        <v>7900</v>
       </c>
       <c r="E66" s="3">
         <v>400</v>
